--- a/docs/DB_스키마.xlsx
+++ b/docs/DB_스키마.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-57600" yWindow="600" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="테이블 목록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="컬럼 정의" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메모" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테이블 목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컬럼 정의" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메모" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -547,7 +547,7 @@
         <t>사용자 행동 데이터(조회 기록, 검색·구매 패턴 분석, AI 추천 모델 학습 데이터 제공).</t>
       </text>
     </comment>
-    <comment ref="B185" authorId="0" shapeId="0">
+    <comment ref="B191" authorId="0" shapeId="0">
       <text>
         <t>서비스(페이지) 만족도 별점(1~5). 주문완료 등에서 수집, ML 피처(satisfaction_score) 원천. 응답률 낮음 전제(미응답 결측).</t>
       </text>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="22" customWidth="1" style="26" min="1" max="1"/>
@@ -864,10 +864,11 @@
     <row r="2">
       <c r="A2" s="28" t="inlineStr">
         <is>
-          <t>총 29개 테이블 · 정리일 2026-07-02 · 위험 유형 8종 확정 반영</t>
-        </is>
-      </c>
-    </row>
+          <t>총 30개 테이블 · 정리일 2026-07-30 · 최종 구현 현황 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1436,7 +1437,7 @@
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" s="26">
-      <c r="A32" s="24" t="n"/>
+      <c r="A32" s="27" t="n"/>
       <c r="B32" s="32" t="inlineStr">
         <is>
           <t>notices</t>
@@ -1453,23 +1454,41 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+    <row r="33" ht="20" customHeight="1" s="26">
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>자주 묻는 질문</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>고객센터 FAQ 조회 / 관리자 등록·수정·삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>만족도</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>satisfaction_survey</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>서비스(페이지) 만족도 별점</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>주문완료 등에서 수집 / ML 피처·이탈 신호 분석</t>
         </is>
@@ -1499,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E195"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="20" customWidth="1" style="26" min="1" max="1"/>
@@ -1516,6 +1535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -5070,7 +5090,7 @@
         </is>
       </c>
     </row>
-    <row r="181">
+    <row r="181" s="26">
       <c r="A181" s="27" t="n"/>
       <c r="B181" s="31" t="inlineStr">
         <is>
@@ -5093,7 +5113,7 @@
         </is>
       </c>
     </row>
-    <row r="182">
+    <row r="182" s="26">
       <c r="A182" s="27" t="n"/>
       <c r="B182" s="27" t="n"/>
       <c r="C182" s="32" t="inlineStr">
@@ -5131,8 +5151,8 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="24" t="n"/>
+    <row r="184" s="26">
+      <c r="A184" s="27" t="n"/>
       <c r="B184" s="24" t="n"/>
       <c r="C184" s="32" t="inlineStr">
         <is>
@@ -5150,120 +5170,238 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="41" t="inlineStr">
-        <is>
-          <t>만족도</t>
-        </is>
-      </c>
-      <c r="B185" s="35" t="inlineStr">
-        <is>
-          <t>satisfaction_survey</t>
-        </is>
-      </c>
-      <c r="C185" s="32" t="inlineStr">
-        <is>
-          <t>survey_id</t>
-        </is>
-      </c>
-      <c r="D185" s="16" t="inlineStr">
+    <row r="185" s="26">
+      <c r="A185" s="27" t="n"/>
+      <c r="B185" s="31" t="inlineStr">
+        <is>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>faq_id</t>
+        </is>
+      </c>
+      <c r="D185" s="18" t="inlineStr">
         <is>
           <t>BIGSERIAL PK</t>
         </is>
       </c>
       <c r="E185" s="17" t="inlineStr">
         <is>
-          <t>만족도번호</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
+          <t>FAQ 번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" s="26">
       <c r="A186" s="27" t="n"/>
       <c r="B186" s="27" t="n"/>
       <c r="C186" s="32" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>question</t>
         </is>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="E186" s="17" t="inlineStr">
         <is>
-          <t>회원</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
+          <t>질문</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" s="26">
       <c r="A187" s="27" t="n"/>
       <c r="B187" s="27" t="n"/>
       <c r="C187" s="32" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>answer</t>
         </is>
       </c>
       <c r="D187" s="16" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E187" s="17" t="inlineStr">
         <is>
-          <t>만족도 점수(1~5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
+          <t>답변</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" s="26">
       <c r="A188" s="27" t="n"/>
       <c r="B188" s="27" t="n"/>
       <c r="C188" s="32" t="inlineStr">
         <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="E188" s="17" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" s="26">
+      <c r="A189" s="27" t="n"/>
+      <c r="B189" s="27" t="n"/>
+      <c r="C189" s="32" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D189" s="16" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E189" s="17" t="inlineStr">
+        <is>
+          <t>작성일</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" s="26">
+      <c r="A190" s="24" t="n"/>
+      <c r="B190" s="24" t="n"/>
+      <c r="C190" s="32" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E190" s="17" t="inlineStr">
+        <is>
+          <t>수정일</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="41" t="inlineStr">
+        <is>
+          <t>만족도</t>
+        </is>
+      </c>
+      <c r="B191" s="35" t="inlineStr">
+        <is>
+          <t>satisfaction_survey</t>
+        </is>
+      </c>
+      <c r="C191" s="32" t="inlineStr">
+        <is>
+          <t>survey_id</t>
+        </is>
+      </c>
+      <c r="D191" s="16" t="inlineStr">
+        <is>
+          <t>BIGSERIAL PK</t>
+        </is>
+      </c>
+      <c r="E191" s="17" t="inlineStr">
+        <is>
+          <t>만족도번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="27" t="n"/>
+      <c r="B192" s="27" t="n"/>
+      <c r="C192" s="32" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E192" s="17" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="27" t="n"/>
+      <c r="B193" s="27" t="n"/>
+      <c r="C193" s="32" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D193" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="E193" s="17" t="inlineStr">
+        <is>
+          <t>만족도 점수(1~5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="27" t="n"/>
+      <c r="B194" s="27" t="n"/>
+      <c r="C194" s="32" t="inlineStr">
+        <is>
           <t>context</t>
         </is>
       </c>
-      <c r="D188" s="16" t="inlineStr">
+      <c r="D194" s="16" t="inlineStr">
         <is>
           <t>VARCHAR(20)</t>
         </is>
       </c>
-      <c r="E188" s="17" t="inlineStr">
+      <c r="E194" s="17" t="inlineStr">
         <is>
           <t>수집 지점: ORDER(주문완료) / CANCEL(해지) / CS</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="24" t="n"/>
-      <c r="B189" s="24" t="n"/>
-      <c r="C189" s="32" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="24" t="n"/>
+      <c r="B195" s="24" t="n"/>
+      <c r="C195" s="32" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D189" s="16" t="inlineStr">
+      <c r="D195" s="16" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="E189" s="17" t="inlineStr">
+      <c r="E195" s="17" t="inlineStr">
         <is>
           <t>평가일</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="46">
     <mergeCell ref="B119:B123"/>
     <mergeCell ref="A97:A108"/>
-    <mergeCell ref="A185:A189"/>
     <mergeCell ref="B53:B57"/>
+    <mergeCell ref="B191:B195"/>
     <mergeCell ref="A77:A82"/>
     <mergeCell ref="B65:B69"/>
+    <mergeCell ref="A38:A49"/>
     <mergeCell ref="B129:B136"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A38:A49"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B124:B128"/>
@@ -5276,15 +5414,14 @@
     <mergeCell ref="A129:A163"/>
     <mergeCell ref="B38:B41"/>
     <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B185:B189"/>
     <mergeCell ref="B181:B184"/>
     <mergeCell ref="B83:B89"/>
+    <mergeCell ref="A191:A195"/>
     <mergeCell ref="B97:B101"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="B147:B154"/>
     <mergeCell ref="B4:B14"/>
-    <mergeCell ref="A164:A184"/>
     <mergeCell ref="A23:A37"/>
     <mergeCell ref="B23:B32"/>
     <mergeCell ref="A119:A123"/>
@@ -5300,6 +5437,8 @@
     <mergeCell ref="A109:A118"/>
     <mergeCell ref="B164:B171"/>
     <mergeCell ref="B58:B64"/>
+    <mergeCell ref="A164:A190"/>
+    <mergeCell ref="B185:B190"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -5312,7 +5451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="100" customWidth="1" style="26" min="1" max="1"/>
@@ -5349,7 +5488,7 @@
     <row r="6" ht="30" customHeight="1" s="26">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>4. 게시판(공지/Q&amp;A) 테이블은 원본 미작성 → notice/qna 별도 문서로 관리.</t>
+          <t>4. 고객지원 테이블은 inquiries(상품/일반 문의) / notices(공지) / faqs(자주 묻는 질문)로 관리.</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5502,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6. CS/알림 테이블 신설: notifications(대응 알림 수신+클릭 추적) / inquiries(상품문의+1:1, 게시판과 별도) / notices(공지). recommendation_history에 shown·clicked·converted·order_id 추가(추천 효과 측정).</t>
+          <t>6. CS/알림 테이블: notifications / inquiries / notices / faqs. recommendation_history에는 shown·clicked·converted·order_id를 사용.</t>
         </is>
       </c>
     </row>
@@ -5388,10 +5527,17 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" s="26">
       <c r="A12" t="inlineStr">
         <is>
           <t>10. PG 연동 확정(토스페이먼츠 테스트 키): orders.payment_key 추가. 결제 플로우 = FE 결제위젯 → successUrl → BE /api/payments/confirm(승인). mock 폴백 유지(데모 리스크 대비). 실결제·정산은 사업자 필요하므로 테스트 모드만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="26">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11. FAQ 테이블 신설(29→30개): 공개 목록 조회와 관리자 등록·수정·삭제에 사용.</t>
         </is>
       </c>
     </row>
